--- a/Result/profitability/2395.xlsx
+++ b/Result/profitability/2395.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.33</v>
       </c>
       <c r="M2" t="n">
-        <v>2.89125</v>
+        <v>3.21375</v>
       </c>
       <c r="N2" t="n">
-        <v>40.525</v>
+        <v>40.0725</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>2.73375</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>40.6375</v>
+        <v>40.19625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.46</v>
       </c>
       <c r="M4" t="n">
-        <v>2.5325</v>
+        <v>2.78625</v>
       </c>
       <c r="N4" t="n">
-        <v>40.7725</v>
+        <v>40.42</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.12</v>
       </c>
       <c r="M5" t="n">
-        <v>2.27625</v>
+        <v>2.63875</v>
       </c>
       <c r="N5" t="n">
-        <v>40.965</v>
+        <v>40.67625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.76</v>
       </c>
       <c r="M6" t="n">
-        <v>2.08375</v>
+        <v>2.33375</v>
       </c>
       <c r="N6" t="n">
-        <v>41.07875</v>
+        <v>40.93</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.72</v>
       </c>
       <c r="M7" t="n">
-        <v>1.77375</v>
+        <v>1.975</v>
       </c>
       <c r="N7" t="n">
-        <v>41.19875</v>
+        <v>40.93625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.11</v>
       </c>
       <c r="M8" t="n">
-        <v>1.46375</v>
+        <v>1.6325</v>
       </c>
       <c r="N8" t="n">
-        <v>41.39875</v>
+        <v>41.215</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>1.0975</v>
       </c>
       <c r="N9" t="n">
-        <v>41.585</v>
+        <v>41.58499999999999</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>26126</v>
+      </c>
+      <c r="D75" t="n">
+        <v>16281</v>
+      </c>
+      <c r="E75" t="n">
+        <v>9845</v>
+      </c>
+      <c r="F75" t="n">
+        <v>37.68</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5127</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>19.63%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>463</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5590</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4518</v>
+      </c>
+      <c r="L75" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.81</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3506493506493507</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.469999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03754789272030645</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.260869565217392</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.310000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.05776444111027768</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
